--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -89,6 +89,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
   </si>
 </sst>
 </file>
@@ -645,19 +663,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -851,7 +869,7 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1066,19 +1084,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -1088,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1118,6 +1136,52 @@
         <v>23</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920094</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920085</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -611,19 +611,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>87.8</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -823,7 +823,7 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1032,19 +1032,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>87.8</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -94,16 +94,25 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>BRAVO</t>
   </si>
   <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
   </si>
   <si>
     <t>DIANA IVONNE</t>
@@ -533,10 +542,10 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>4</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>32</v>
@@ -545,7 +554,7 @@
         <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -611,10 +620,10 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>37</v>
@@ -623,7 +632,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -663,19 +672,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -728,16 +737,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -751,16 +763,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>58.33</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -774,16 +789,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -797,16 +815,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -820,16 +841,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>9.76</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -843,16 +867,19 @@
         <v>16</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>16</v>
       </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -866,16 +893,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>96.88</v>
+      </c>
+      <c r="H8">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +970,7 @@
         <v>91.67</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -954,10 +984,10 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>4</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>32</v>
@@ -966,7 +996,7 @@
         <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -983,16 +1013,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1009,16 +1039,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1032,10 +1062,10 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>37</v>
@@ -1044,7 +1074,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1070,7 +1100,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1084,19 +1114,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1144,10 +1174,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1161,24 +1191,47 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920085</v>
+        <v>21330051920115</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920085</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -91,31 +91,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
   </si>
   <si>
     <t>BRAVO</t>
   </si>
   <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
   </si>
   <si>
     <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
   </si>
 </sst>
 </file>
@@ -763,19 +772,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>58.33</v>
+        <v>77.78</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -841,19 +850,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>9.76</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -893,19 +902,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -987,13 +996,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
         <v>7.8</v>
@@ -1065,16 +1074,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>90.23999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1117,13 +1126,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>8.800000000000001</v>
@@ -1136,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1168,22 +1177,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920094</v>
+        <v>21330051920115</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1191,22 +1200,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920115</v>
+        <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1214,24 +1223,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920085</v>
+        <v>21330051920041</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920094</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -772,19 +772,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>77.78</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -850,19 +850,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>68.29000000000001</v>
+        <v>75.61</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1083,7 +1083,7 @@
         <v>85.37</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -91,40 +91,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
   </si>
   <si>
     <t>ESTRADA</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
     <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -746,7 +737,7 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -850,16 +841,16 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -970,16 +961,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -996,13 +987,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H3">
         <v>7.8</v>
@@ -1022,16 +1013,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1057,7 +1048,7 @@
         <v>92.86</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1083,7 +1074,7 @@
         <v>85.37</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1109,7 +1100,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1135,7 +1126,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1177,22 +1168,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920115</v>
+        <v>21330051920094</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1200,16 +1191,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920032</v>
+        <v>21330051920388</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1223,16 +1214,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920041</v>
+        <v>21330051920039</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1242,29 +1233,6 @@
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920094</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -94,28 +94,10 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>BRAVO</t>
   </si>
   <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
     <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1174,10 +1156,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1186,52 +1168,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920388</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920039</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>
